--- a/SGC-CKN/Excel/cbaa4c19-b94d-4f8c-a712-4a7eaac3cd41_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-19_D800_04-04-2026.xlsx
+++ b/SGC-CKN/Excel/cbaa4c19-b94d-4f8c-a712-4a7eaac3cd41_Thi_công_cọc_khoan_nhồi__tường_vây_cho_các_hạng_mục_Lô_CT-02_P1-19_D800_04-04-2026.xlsx
@@ -216,7 +216,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -253,6 +253,12 @@
     </font>
     <font>
       <color rgb="FF78350F"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -299,7 +305,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,6 +340,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -464,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -502,23 +513,17 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -556,13 +561,22 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1186,245 +1200,245 @@
         <v>-2.4</v>
       </c>
       <c r="G12" s="9">
-        <v>-5.5</v>
+        <v>-3.5</v>
       </c>
       <c r="H12" s="9">
         <v>1.5</v>
       </c>
       <c r="I12" s="9">
-        <v>3.1</v>
-      </c>
-      <c r="J12" s="8">
-        <v>2.07</v>
+        <v>1.1</v>
+      </c>
+      <c r="J12" s="12">
+        <v>0.73</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="12">
-        <v>-5.5</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="F13" s="13">
+        <v>-3.5</v>
+      </c>
+      <c r="G13" s="13">
         <v>-8.8</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <v>0.5</v>
       </c>
-      <c r="I13" s="12">
-        <v>3.3</v>
-      </c>
-      <c r="J13" s="15">
-        <v>6.6</v>
-      </c>
-      <c r="K13" s="13" t="s">
+      <c r="I13" s="13">
+        <v>5.3</v>
+      </c>
+      <c r="J13" s="16">
+        <v>10.6</v>
+      </c>
+      <c r="K13" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="17">
         <v>-8.8</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="17">
         <v>-13</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="17">
         <v>1</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="17">
         <v>4.2</v>
       </c>
       <c r="J14" s="8">
         <v>4.2</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="18" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="20">
         <v>-13</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="20">
         <v>-20</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="20">
         <v>0.92</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="20">
         <v>7</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="16">
         <v>7.64</v>
       </c>
-      <c r="K15" s="20" t="s">
+      <c r="K15" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="23">
         <v>-20</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="23">
         <v>-26.2</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="23">
         <v>1.08</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="23">
         <v>6.2</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="16">
         <v>5.72</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="24" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <v>-26.2</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="26">
         <v>-39</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="26">
         <v>3.33</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="26">
         <v>12.8</v>
       </c>
       <c r="J17" s="8">
         <v>3.84</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="27" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="29">
         <v>-39</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="29">
         <v>-44.45</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="29">
         <v>2.1</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="29">
         <v>5.45</v>
       </c>
       <c r="J18" s="8">
         <v>2.6</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K18" s="30" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1592,70 +1606,70 @@
         <v>-2.4</v>
       </c>
       <c r="F3" s="9">
-        <v>-5.5</v>
+        <v>-3.5</v>
       </c>
       <c r="G3" s="9">
         <v>1.5</v>
       </c>
       <c r="H3" s="9">
-        <v>3.1</v>
-      </c>
-      <c r="I3" s="8">
-        <v>2.07</v>
+        <v>1.1</v>
+      </c>
+      <c r="I3" s="12">
+        <v>0.73</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="12">
-        <v>-5.5</v>
-      </c>
-      <c r="F4" s="12">
+      <c r="E4" s="13">
+        <v>-3.5</v>
+      </c>
+      <c r="F4" s="13">
         <v>-8.8</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="13">
         <v>0.5</v>
       </c>
-      <c r="H4" s="12">
-        <v>3.3</v>
-      </c>
-      <c r="I4" s="15">
-        <v>6.6</v>
+      <c r="H4" s="13">
+        <v>5.3</v>
+      </c>
+      <c r="I4" s="16">
+        <v>10.6</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="17">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="17">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="17">
         <v>-8.8</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="17">
         <v>-13</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="17">
         <v>1</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="17">
         <v>4.2</v>
       </c>
       <c r="I5" s="8">
@@ -1663,86 +1677,86 @@
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="20">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <v>-13</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <v>-20</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <v>0.92</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="20">
         <v>7</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="16">
         <v>7.64</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="23">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="23">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="23">
         <v>-20</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="23">
         <v>-26.2</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="23">
         <v>1.08</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="23">
         <v>6.2</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="16">
         <v>5.72</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="26">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>-26.2</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>-39</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="26">
         <v>3.33</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="26">
         <v>12.8</v>
       </c>
       <c r="I8" s="8">
@@ -1750,28 +1764,28 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
+      <c r="A9" s="29">
         <v>8</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <v>1</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <v>-39</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <v>-44.45</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="29">
         <v>2.1</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="29">
         <v>5.45</v>
       </c>
       <c r="I9" s="8">
@@ -1779,31 +1793,31 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <v>8</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="34">
         <v>0</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="34">
         <v>-44.45</v>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="34">
         <v>10.93</v>
       </c>
-      <c r="H10" s="33">
+      <c r="H10" s="34">
         <v>44.45</v>
       </c>
-      <c r="I10" s="33">
+      <c r="I10" s="34">
         <v>4.07</v>
       </c>
     </row>
